--- a/plantillas/Layout_Carga_Fideicomisos_BX.xlsx
+++ b/plantillas/Layout_Carga_Fideicomisos_BX.xlsx
@@ -1601,9 +1601,6 @@
     <dataValidation sqref="J2:J1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
       <formula1>=CATÁLOGOS!$H$2:$H$4</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
-      <formula1>=CATÁLOGOS!$K$2:$K$11</formula1>
-    </dataValidation>
     <dataValidation sqref="M2:M1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
       <formula1>=CATÁLOGOS!$I$2:$I$7</formula1>
     </dataValidation>
@@ -1625,9 +1622,6 @@
     <dataValidation sqref="S2:S1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
       <formula1>=CATÁLOGOS!$M$2:$M$6</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
-      <formula1>=CATÁLOGOS!$N$2:$N$5</formula1>
-    </dataValidation>
     <dataValidation sqref="U2:U1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Solo SI o NO." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
@@ -1636,6 +1630,12 @@
     </dataValidation>
     <dataValidation sqref="W2:W1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Solo SI o NO." type="list">
       <formula1>"SI,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=CATÁLOGOS!$O$2:$O$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=CATÁLOGOS!$N$2:$N$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1648,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1735,7 +1735,12 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>Antigüedad parte</t>
+          <t>Edad / antigüedad parte</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Actividad del fideicomiso</t>
         </is>
       </c>
     </row>
@@ -1810,6 +1815,11 @@
           <t>Más de 10 años</t>
         </is>
       </c>
+      <c r="O2" s="11" t="inlineStr">
+        <is>
+          <t>Tenencia / administración patrimonial estática</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -1882,6 +1892,11 @@
           <t>3 a 10 años</t>
         </is>
       </c>
+      <c r="O3" s="11" t="inlineStr">
+        <is>
+          <t>Prestaciones laborales (fondos de ahorro / pensiones)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -1954,6 +1969,11 @@
           <t>1 a 3 años</t>
         </is>
       </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Planeación patrimonial / sucesorio-testamentario</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -2011,6 +2031,11 @@
           <t>Menos de 1 año</t>
         </is>
       </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>Garantía o fuente de pago de financiamiento</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -2053,6 +2078,16 @@
           <t>Frontera / puerto</t>
         </is>
       </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>25 a 50 años</t>
+        </is>
+      </c>
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>Administración de inversiones y valores</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -2080,6 +2115,16 @@
           <t>Lista GAFI negra / sancionado</t>
         </is>
       </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>51 a 65 años</t>
+        </is>
+      </c>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Inmobiliario: adquisición en zona restringida</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -2092,6 +2137,16 @@
           <t>Inmobiliario / construcción</t>
         </is>
       </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Más de 65 años</t>
+        </is>
+      </c>
+      <c r="O8" s="11" t="inlineStr">
+        <is>
+          <t>No capturada</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -2104,6 +2159,16 @@
           <t>Entidad auxiliar del crédito (SOFOM/SOFIPO/arrendadora/aseguradora)</t>
         </is>
       </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>18 a 24 años</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>Arrendamiento de inmuebles (Fracc. XV LFPIORPI)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="K10" s="11" t="inlineStr">
@@ -2111,11 +2176,54 @@
           <t>Comercio exterior</t>
         </is>
       </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>Menor de edad</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>Recepción de donativos / asistencia social (Fracc. XIII)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="K11" s="12" t="inlineStr">
         <is>
           <t>Efectivo intensivo</t>
+        </is>
+      </c>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>Otorgamiento de préstamos o créditos (Fracc. IV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>Comercio exterior / pagos internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>Entidad auxiliar del crédito como parte del negocio (SOFOM/SOFIPO/arrendadora/aseguradora)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>Desarrollo inmobiliario: construcción y venta (Fracc. V / V Bis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>Manejo intensivo de efectivo</t>
         </is>
       </c>
     </row>

--- a/plantillas/Layout_Carga_Fideicomisos_BX.xlsx
+++ b/plantillas/Layout_Carga_Fideicomisos_BX.xlsx
@@ -1604,9 +1604,6 @@
     <dataValidation sqref="M2:M1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
       <formula1>=CATÁLOGOS!$I$2:$I$7</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
-      <formula1>=CATÁLOGOS!$J$2:$J$7</formula1>
-    </dataValidation>
     <dataValidation sqref="O2:O1500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fuera de catálogo" error="Elija un valor de la lista (hoja CATÁLOGOS)." type="list">
       <formula1>=CATÁLOGOS!$K$2:$K$11</formula1>
     </dataValidation>
@@ -1636,6 +1633,9 @@
     </dataValidation>
     <dataValidation sqref="T2:T1500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=CATÁLOGOS!$N$2:$N$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=CATÁLOGOS!$J$2:$J$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>PF nacional</t>
+          <t>Persona física</t>
         </is>
       </c>
       <c r="K2" s="11" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>PM nacional</t>
+          <t>Persona moral</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>PM extranjera</t>
+          <t>Fideicomiso / vehículo</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
@@ -2100,11 +2100,7 @@
           <t>Fideicomitente-Fideicomisario</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Fideicomiso / vehículo</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="inlineStr">
         <is>
           <t>No capturada</t>
